--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/back_20gps_summary.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/back_20gps_summary.xlsx
@@ -14,12 +14,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Velocity (m/s)</t>
   </si>
   <si>
     <t>Q_steady (W)</t>
+  </si>
+  <si>
+    <t>Q_uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -351,71 +354,95 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>221.3957719718514</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>222.8496763553217</v>
+      </c>
+      <c r="C2">
+        <v>32.77362820046438</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>406.0431682390105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>407.8262252772824</v>
+      </c>
+      <c r="C3">
+        <v>32.64973087008466</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>530.4446240851555</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>531.6681670040086</v>
+      </c>
+      <c r="C4">
+        <v>32.59461441848617</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>610.0047056400032</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>610.9029364763509</v>
+      </c>
+      <c r="C5">
+        <v>32.58811231863646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>680.0717004874964</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>679.8819109525917</v>
+      </c>
+      <c r="C6">
+        <v>32.51764504822712</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>720.1188749472599</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>718.9046521765575</v>
+      </c>
+      <c r="C7">
+        <v>32.4658925690079</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>756.3550818637028</v>
+        <v>760.3749601665666</v>
+      </c>
+      <c r="C8">
+        <v>32.48314309845292</v>
       </c>
     </row>
   </sheetData>
